--- a/data/google/Keyword/Keyword-July-week4.xlsx
+++ b/data/google/Keyword/Keyword-July-week4.xlsx
@@ -70,7 +70,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>July 21, 2026 - July 23, 2026</t>
+          <t>July 21, 2026 - July 27, 2026</t>
         </is>
       </c>
     </row>
@@ -154,7 +154,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>"ทอง 99.99 ออ โร ร่า"</t>
+          <t>"โปร aurora"</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -191,7 +191,7 @@
         <v>0.0</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="K4" s="1" t="n">
         <v>0.0</v>
@@ -199,15 +199,11 @@
       <c r="L4" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+      <c r="M4" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>1.0</v>
       </c>
     </row>
     <row r="5">
@@ -218,7 +214,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>"ทองวันนี้"</t>
+          <t>"แหวน ทอง 1 กรัม aurora"</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -233,7 +229,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>Generic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -252,22 +248,26 @@
         </is>
       </c>
       <c r="I5" s="1" t="n">
-        <v>22.75</v>
+        <v>0.0</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>243.0</v>
+        <v>0.0</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>37.0</v>
+        <v>0.0</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>0.1523</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>0.4563</v>
+        <v>0.0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -278,7 +278,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>"ออโรร่า ใกล้ฉัน"</t>
+          <t>"แบรนด์ aurora"</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -293,7 +293,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>Generic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -312,22 +312,26 @@
         </is>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.52</v>
+        <v>0.0</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>32.0</v>
+        <v>0.0</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>0.0313</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>0.3571</v>
+        <v>0.0</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -338,7 +342,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>"ซื้อขาย ทอง ออนไลน์ ออ โร ร่า"</t>
+          <t>"aurora gold สาขา"</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -375,7 +379,7 @@
         <v>0.0</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>0.0</v>
@@ -383,15 +387,11 @@
       <c r="L7" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+      <c r="M7" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>1.0</v>
       </c>
     </row>
     <row r="8">
@@ -402,7 +402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>"ราคาทอง ร้านทองเยาวราช กรุงเทพ"</t>
+          <t>"กุหลาบ ทอง ออ โร ร่า"</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -417,7 +417,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>Generic</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -466,7 +466,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>"ห้างทองเยาวราช ราคาทอง"</t>
+          <t>"aurora ทอง สาขา"</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -481,7 +481,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>Generic</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>"สมาคมทองคำ"</t>
+          <t>"ทอง แท่ง 5 บาท ออ โร ร่า"</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -545,7 +545,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>Generic</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>"ร้านขายทอง"</t>
+          <t>"ของขวัญ วัน เกิด ทอง"</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>Generic</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -631,7 +631,7 @@
         <v>0.0</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>0.0</v>
@@ -639,11 +639,15 @@
       <c r="L11" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="M11" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>0.3333</v>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -654,7 +658,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>"ของขวัญ วัน เกิด ทอง"</t>
+          <t>"ราคา ทอง 1 สลึง วัน นี้ aurora"</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -718,7 +722,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>"ราคาทองห้างเยาวราช"</t>
+          <t>"พระ เลี่ยม ทอง ออ โร ร่า"</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -733,7 +737,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>Generic</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -755,7 +759,7 @@
         <v>0.0</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>0.0</v>
@@ -763,11 +767,15 @@
       <c r="L13" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="M13" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>1.0</v>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -778,7 +786,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>"ร้านทองออนไลน์"</t>
+          <t>"สร้อยทอง 2 สลึง"</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -793,7 +801,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>Generic</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -812,26 +820,22 @@
         </is>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.0</v>
+        <v>0.38</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.0</v>
+        <v>47.0</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+        <v>0.38</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="15">
@@ -842,7 +846,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>"aurora gold สาขา"</t>
+          <t>"สร้อย สามกษัตริย์ ออ โร ร่า"</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -906,7 +910,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>"ร้านเพชรทองออโรร่า"</t>
+          <t>"ทอง 99.99 ออ โร ร่า"</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -921,7 +925,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>Generic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -940,22 +944,26 @@
         </is>
       </c>
       <c r="I16" s="1" t="n">
-        <v>0.52</v>
+        <v>0.0</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>0.9</v>
+        <v>0.0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -966,12 +974,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ห้างทองใกล้ฉัน</t>
+          <t>"ซื้อขาย ทอง ออนไลน์ ออ โร ร่า"</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Broad match</t>
+          <t>Phrase match</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -981,7 +989,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>Generic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1000,22 +1008,22 @@
         </is>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>156.0</v>
+        <v>1.0</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>0.44</v>
+        <v>0.92</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0.0128</v>
+        <v>1.0</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.5714</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="18">
@@ -1026,12 +1034,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>"ร้านทองเยาวราช"</t>
+          <t>[Gold now]</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phrase match</t>
+          <t>Exact match</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1060,22 +1068,22 @@
         </is>
       </c>
       <c r="I18" s="1" t="n">
-        <v>7.54</v>
+        <v>0.0</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>279.0</v>
+        <v>2.0</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>1.08</v>
+        <v>0.0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>0.0251</v>
+        <v>0.0</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="19">
@@ -1086,7 +1094,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>"ราคา ทอง 1 สลึง วัน นี้ aurora"</t>
+          <t>"ราคาทอง ร้านทองเยาวราช กรุงเทพ"</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1101,7 +1109,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generic</t>
+          <t>Brand</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1150,12 +1158,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>"ราคาทอง"</t>
+          <t>[ห้างทองเยาวราช]</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phrase match</t>
+          <t>Exact match</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1184,22 +1192,22 @@
         </is>
       </c>
       <c r="I20" s="1" t="n">
-        <v>293.03</v>
+        <v>0.0</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>3121.0</v>
+        <v>13.0</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>557.0</v>
+        <v>0.0</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>0.53</v>
+        <v>0.0</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>0.1785</v>
+        <v>0.0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.5142</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="21">
@@ -1210,7 +1218,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"สร้อย สามกษัตริย์ ออ โร ร่า"</t>
+          <t>"ร้านทอง เซ็นทรัล"</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1225,7 +1233,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generic</t>
+          <t>Brand</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1244,26 +1252,22 @@
         </is>
       </c>
       <c r="I21" s="1" t="n">
-        <v>0.0</v>
+        <v>67.56</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>0.0</v>
+        <v>449.0</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>0.0</v>
+        <v>63.0</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+        <v>1.07</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>0.1403</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>0.4773</v>
       </c>
     </row>
     <row r="22">
@@ -1274,7 +1278,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>"เลี่ยมพระ ร้านทอง"</t>
+          <t>"กรอบพระ ร้านทอง"</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1311,7 +1315,7 @@
         <v>0.0</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>0.0</v>
+        <v>49.0</v>
       </c>
       <c r="K22" s="1" t="n">
         <v>0.0</v>
@@ -1319,15 +1323,11 @@
       <c r="L22" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+      <c r="M22" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="23">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[ทองคำราคา]</t>
+          <t>"ราคาทองห้างเยาวราช"</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Exact match</t>
+          <t>Phrase match</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1372,22 +1372,22 @@
         </is>
       </c>
       <c r="I23" s="1" t="n">
-        <v>3.08</v>
+        <v>0.0</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>66.0</v>
+        <v>1.0</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>0.31</v>
+        <v>0.0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0.1515</v>
+        <v>0.0</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.4545</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="24">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>"ห้างทองเยาวราช ราคา"</t>
+          <t>"ราคาทอง ร้านทองเยาวราช"</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1435,7 +1435,7 @@
         <v>0.0</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>0.0</v>
@@ -1443,11 +1443,15 @@
       <c r="L24" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="M24" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N24" s="2" t="n">
-        <v>0.0</v>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1458,12 +1462,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[Gold now]</t>
+          <t>"ร้านทอง โรบินสัน"</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Exact match</t>
+          <t>Phrase match</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1492,26 +1496,22 @@
         </is>
       </c>
       <c r="I25" s="1" t="n">
-        <v>0.0</v>
+        <v>3.96</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>0.0</v>
+        <v>44.0</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+        <v>0.66</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>0.1364</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>0.48</v>
       </c>
     </row>
     <row r="26">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>"ทองกรุงเทพเยาวราช"</t>
+          <t>"ห้าง ทอง ใกล้ ฉัน"</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1556,24 +1556,22 @@
         </is>
       </c>
       <c r="I26" s="1" t="n">
-        <v>0.0</v>
+        <v>0.78</v>
       </c>
       <c r="J26" s="1" t="n">
+        <v>216.0</v>
+      </c>
+      <c r="K26" s="1" t="n">
         <v>1.0</v>
       </c>
-      <c r="K26" s="1" t="n">
-        <v>0.0</v>
-      </c>
       <c r="L26" s="1" t="n">
-        <v>0.0</v>
+        <v>0.78</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+        <v>0.0046</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>0.375</v>
       </c>
     </row>
     <row r="27">
@@ -1584,12 +1582,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[ห้าง ทอง ใกล้ ฉัน]</t>
+          <t>"ร้านทอง ซีคอน"</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Exact match</t>
+          <t>Phrase match</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1604,12 +1602,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Eligible</t>
+          <t>Limited</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t/>
+          <t>low quality</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1618,22 +1616,22 @@
         </is>
       </c>
       <c r="I27" s="1" t="n">
-        <v>0.42</v>
+        <v>0.0</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>57.0</v>
+        <v>14.0</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>0.42</v>
+        <v>0.0</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>0.0175</v>
+        <v>0.0</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="28">
@@ -1644,12 +1642,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[Bangkok Golds]</t>
+          <t>"ราคาทอง"</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Exact match</t>
+          <t>Phrase match</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1678,26 +1676,22 @@
         </is>
       </c>
       <c r="I28" s="1" t="n">
-        <v>0.0</v>
+        <v>875.74</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>0.0</v>
+        <v>8253.0</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>0.0</v>
+        <v>1372.0</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+        <v>0.64</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>0.1662</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>0.5352</v>
       </c>
     </row>
     <row r="29">
@@ -1708,12 +1702,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[ห้างทองเยาวราชกรุงเทพ]</t>
+          <t>"ทองวันนี้"</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Exact match</t>
+          <t>Phrase match</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1742,24 +1736,22 @@
         </is>
       </c>
       <c r="I29" s="1" t="n">
-        <v>0.0</v>
+        <v>65.5</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>4.0</v>
+        <v>616.0</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>0.0</v>
+        <v>85.0</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>0.0</v>
+        <v>0.77</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+        <v>0.138</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>0.4822</v>
       </c>
     </row>
     <row r="30">
@@ -1770,12 +1762,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>"พระ เลี่ยม ทอง ออ โร ร่า"</t>
+          <t>[ห้างทองเยาวราชกรุงเทพ]</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phrase match</t>
+          <t>Exact match</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1785,7 +1777,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Generic</t>
+          <t>Brand</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1807,7 +1799,7 @@
         <v>0.0</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="K30" s="1" t="n">
         <v>0.0</v>
@@ -1815,10 +1807,8 @@
       <c r="L30" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+      <c r="M30" s="2" t="n">
+        <v>0.0</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -1834,12 +1824,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[ห้าง ทอง เยาวราช กรุงเทพ ใกล้ ฉัน]</t>
+          <t>"ราคาทองวันนี้"</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Exact match</t>
+          <t>Phrase match</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1868,24 +1858,22 @@
         </is>
       </c>
       <c r="I31" s="1" t="n">
-        <v>0.0</v>
+        <v>517.81</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>3.0</v>
+        <v>4978.0</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>0.0</v>
+        <v>793.0</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>0.0</v>
+        <v>0.65</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+        <v>0.1593</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>0.4692</v>
       </c>
     </row>
     <row r="32">
@@ -1896,12 +1884,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>"ร้านทอง เซ็นทรัล"</t>
+          <t>[ห้างทองแม่ทองสุก]</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Phrase match</t>
+          <t>Exact match</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1930,22 +1918,22 @@
         </is>
       </c>
       <c r="I32" s="1" t="n">
-        <v>2.41</v>
+        <v>0.0</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>65.0</v>
+        <v>34.0</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>0.3</v>
+        <v>0.0</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>0.1231</v>
+        <v>0.0</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.4688</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="33">
@@ -1956,7 +1944,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>"ทองแท่ง เยาวราช กรุงเทพ"</t>
+          <t>"ร้านเพชรทองออโรร่า"</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1990,37 +1978,33 @@
         </is>
       </c>
       <c r="I33" s="1" t="n">
-        <v>0.0</v>
+        <v>6.61</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>0.0</v>
+        <v>52.0</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+        <v>0.51</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>0.8511</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Enabled</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>"ร้านทอ"</t>
+          <t>"www hua seng heng com"</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2040,12 +2024,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Eligible</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>paused</t>
+          <t/>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2084,7 +2068,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>"ทอง แท่ง 5 บาท ออ โร ร่า"</t>
+          <t>"ราคา ห้างทองเยาวราช"</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2099,7 +2083,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Generic</t>
+          <t>Brand</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2148,12 +2132,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>"aurora ทอง สาขา"</t>
+          <t>[aurora]</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Phrase match</t>
+          <t>Exact match</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2163,7 +2147,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Generic</t>
+          <t>Brand</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2182,26 +2166,22 @@
         </is>
       </c>
       <c r="I36" s="1" t="n">
-        <v>0.0</v>
+        <v>189.15</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>0.0</v>
+        <v>1023.0</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>0.0</v>
+        <v>534.0</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+        <v>0.35</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>0.9585</v>
       </c>
     </row>
     <row r="37">
@@ -2212,12 +2192,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>"ร้านทอง โลตัส"</t>
+          <t>[ห้าง ทอง เยาวราช กรุงเทพ]</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Phrase match</t>
+          <t>Exact match</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2246,26 +2226,22 @@
         </is>
       </c>
       <c r="I37" s="1" t="n">
-        <v>0.0</v>
+        <v>0.77</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>0.0</v>
+        <v>56.0</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+        <v>0.77</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>0.6667</v>
       </c>
     </row>
     <row r="38">
@@ -2276,12 +2252,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[แม่ ทอง สุก]</t>
+          <t>"ทองกรุงเทพเยาวราช"</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Exact match</t>
+          <t>Phrase match</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2313,7 +2289,7 @@
         <v>0.0</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>83.0</v>
+        <v>7.0</v>
       </c>
       <c r="K38" s="1" t="n">
         <v>0.0</v>
@@ -2324,8 +2300,10 @@
       <c r="M38" s="2" t="n">
         <v>0.0</v>
       </c>
-      <c r="N38" s="2" t="n">
-        <v>0.25</v>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -2336,7 +2314,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>"กุหลาบ ทอง ออ โร ร่า"</t>
+          <t>"ห้าง ทอง ทอง เยาวราช"</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2351,7 +2329,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Generic</t>
+          <t>Brand</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2370,26 +2348,22 @@
         </is>
       </c>
       <c r="I39" s="1" t="n">
-        <v>0.0</v>
+        <v>3.61</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>0.0</v>
+        <v>194.0</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+        <v>0.9</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="40">
@@ -2400,12 +2374,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[ห้างทองเยาวราช]</t>
+          <t>"ร้านทอง เปิดวันอาทิตย์"</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Exact match</t>
+          <t>Phrase match</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2434,22 +2408,22 @@
         </is>
       </c>
       <c r="I40" s="1" t="n">
-        <v>0.0</v>
+        <v>5.36</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>0.0</v>
+        <v>5.36</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>0.0</v>
+        <v>0.1111</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>1.0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="41">
@@ -2460,7 +2434,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[ห้างทองแม่ทองสุก]</t>
+          <t>[ฮั่วเซ่งเฮง]</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2494,22 +2468,22 @@
         </is>
       </c>
       <c r="I41" s="1" t="n">
-        <v>0.0</v>
+        <v>0.46</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>12.0</v>
+        <v>242.0</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>0.0</v>
+        <v>0.46</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>0.0</v>
+        <v>0.0041</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0</v>
+        <v>0.2444</v>
       </c>
     </row>
     <row r="42">
@@ -2520,12 +2494,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>"กรอบพระ ร้านทอง"</t>
+          <t>[ร้าน ทอง ใกล้ ฉัน]</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Phrase match</t>
+          <t>Exact match</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2554,24 +2528,22 @@
         </is>
       </c>
       <c r="I42" s="1" t="n">
-        <v>0.0</v>
+        <v>66.34</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>3.0</v>
+        <v>555.0</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>0.0</v>
+        <v>51.0</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>0.0</v>
+        <v>1.3</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+        <v>0.0919</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>0.6484</v>
       </c>
     </row>
     <row r="43">
@@ -2582,7 +2554,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>"ร้านทอง โรบินสัน"</t>
+          <t>"ทองแท่ง เยาวราช กรุงเทพ"</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2619,7 +2591,7 @@
         <v>0.0</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K43" s="1" t="n">
         <v>0.0</v>
@@ -2627,11 +2599,15 @@
       <c r="L43" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="M43" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N43" s="2" t="n">
-        <v>1.0</v>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -2642,7 +2618,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[Hua Seng Heng]</t>
+          <t>[แม่ทองใบ]</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2679,7 +2655,7 @@
         <v>0.0</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
       <c r="K44" s="1" t="n">
         <v>0.0</v>
@@ -2690,8 +2666,10 @@
       <c r="M44" s="2" t="n">
         <v>0.0</v>
       </c>
-      <c r="N44" s="2" t="n">
-        <v>0.0</v>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -2702,12 +2680,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>"ราคา ห้างทองเยาวราช"</t>
+          <t>[ห้าง ทอง ออ โร ร่า ใกล้ ฉัน]</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Phrase match</t>
+          <t>Exact match</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2736,26 +2714,22 @@
         </is>
       </c>
       <c r="I45" s="1" t="n">
-        <v>0.0</v>
+        <v>5.76</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>0.0</v>
+        <v>38.0</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+        <v>0.96</v>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>0.1579</v>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>0.6087</v>
       </c>
     </row>
     <row r="46">
@@ -2766,7 +2740,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>"โปร aurora"</t>
+          <t>"ร้านทอง บิ๊กซี"</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2781,7 +2755,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Generic</t>
+          <t>Brand</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2800,22 +2774,22 @@
         </is>
       </c>
       <c r="I46" s="1" t="n">
-        <v>0.0</v>
+        <v>3.07</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>1.0</v>
+        <v>29.0</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>0.0</v>
+        <v>1.02</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>0.0</v>
+        <v>0.1034</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>1.0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="47">
@@ -2860,22 +2834,22 @@
         </is>
       </c>
       <c r="I47" s="1" t="n">
-        <v>0.7</v>
+        <v>7.45</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>211.0</v>
+        <v>817.0</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>0.35</v>
+        <v>0.68</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>0.0095</v>
+        <v>0.0135</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.3</v>
+        <v>0.5098</v>
       </c>
     </row>
     <row r="48">
@@ -2886,12 +2860,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[แม่ทองใบ]</t>
+          <t>"ร้านขายทอง"</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Exact match</t>
+          <t>Phrase match</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2920,26 +2894,22 @@
         </is>
       </c>
       <c r="I48" s="1" t="n">
-        <v>0.0</v>
+        <v>23.35</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>0.0</v>
+        <v>308.0</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+        <v>1.17</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>0.0649</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>0.6667</v>
       </c>
     </row>
     <row r="49">
@@ -2950,7 +2920,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>"ร้านทองใกล้ฉัน"</t>
+          <t>"เลี่ยมพระ ร้านทอง"</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2984,22 +2954,26 @@
         </is>
       </c>
       <c r="I49" s="1" t="n">
-        <v>1.2</v>
+        <v>0.0</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>113.0</v>
+        <v>0.0</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M49" s="2" t="n">
-        <v>0.0177</v>
-      </c>
-      <c r="N49" s="2" t="n">
-        <v>0.5</v>
+        <v>0.0</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -3010,7 +2984,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>"ร้านทอง บิ๊กซี"</t>
+          <t>"ออโรร่า ใกล้ฉัน"</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3044,26 +3018,22 @@
         </is>
       </c>
       <c r="I50" s="1" t="n">
-        <v>0.0</v>
+        <v>10.32</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>0.0</v>
+        <v>112.0</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+        <v>0.86</v>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>0.1071</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>0.4118</v>
       </c>
     </row>
     <row r="51">
@@ -3074,12 +3044,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>"ซื้อทองออนไลน์"</t>
+          <t>[Hua Seng Heng]</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Phrase match</t>
+          <t>Exact match</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3108,22 +3078,22 @@
         </is>
       </c>
       <c r="I51" s="1" t="n">
-        <v>0.15</v>
+        <v>4.63</v>
       </c>
       <c r="J51" s="1" t="n">
-        <v>21.0</v>
+        <v>163.0</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>0.15</v>
+        <v>0.93</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>0.0476</v>
+        <v>0.0307</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.75</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="52">
@@ -3134,12 +3104,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>"แอปทอง ออนไลน์"</t>
+          <t>[ทองคำราคา]</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Phrase match</t>
+          <t>Exact match</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3168,26 +3138,22 @@
         </is>
       </c>
       <c r="I52" s="1" t="n">
-        <v>0.0</v>
+        <v>43.79</v>
       </c>
       <c r="J52" s="1" t="n">
-        <v>0.0</v>
+        <v>555.0</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>0.0</v>
+        <v>72.0</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+        <v>0.61</v>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>0.1297</v>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>0.547</v>
       </c>
     </row>
     <row r="53">
@@ -3198,12 +3164,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>"ร้านทอง ซีคอน"</t>
+          <t>[ห้าง ทอง ใกล้ ฉัน]</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Phrase match</t>
+          <t>Exact match</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3218,12 +3184,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Limited</t>
+          <t>Eligible</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>low quality</t>
+          <t/>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3232,26 +3198,22 @@
         </is>
       </c>
       <c r="I53" s="1" t="n">
-        <v>0.0</v>
+        <v>2.67</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>0.0</v>
+        <v>171.0</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+        <v>0.67</v>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>0.0234</v>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>0.6667</v>
       </c>
     </row>
     <row r="54">
@@ -3262,12 +3224,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>"ร้านห้างทองเยาวราช"</t>
+          <t>[แม่ ทอง สุก]</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Phrase match</t>
+          <t>Exact match</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3296,26 +3258,22 @@
         </is>
       </c>
       <c r="I54" s="1" t="n">
-        <v>0.0</v>
+        <v>1.17</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>0.0</v>
+        <v>161.0</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+        <v>1.17</v>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="55">
@@ -3326,12 +3284,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>"ห้าง ทอง ใกล้ ฉัน"</t>
+          <t>ห้างทองใกล้ฉัน</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Phrase match</t>
+          <t>Broad match</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3360,24 +3318,22 @@
         </is>
       </c>
       <c r="I55" s="1" t="n">
-        <v>0.0</v>
+        <v>27.21</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>48.0</v>
+        <v>1082.0</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>0.0</v>
+        <v>29.0</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>0.0</v>
+        <v>0.94</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+        <v>0.0268</v>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>0.5323</v>
       </c>
     </row>
     <row r="56">
@@ -3388,7 +3344,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>[ห้างทองฮั่วเซ่งเฮง]</t>
+          <t>[แม่ทองสุก]</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3408,12 +3364,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Limited</t>
+          <t>Eligible</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>low quality</t>
+          <t/>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3422,19 +3378,19 @@
         </is>
       </c>
       <c r="I56" s="1" t="n">
-        <v>0.0</v>
+        <v>0.83</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>21.0</v>
+        <v>47.0</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>0.0</v>
+        <v>0.83</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>0.0</v>
+        <v>0.0213</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -3450,12 +3406,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>[ร้าน ทอง ใกล้ ฉัน]</t>
+          <t>"ร้านห้างทองเยาวราช"</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Exact match</t>
+          <t>Phrase match</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3484,22 +3440,24 @@
         </is>
       </c>
       <c r="I57" s="1" t="n">
-        <v>5.49</v>
+        <v>0.99</v>
       </c>
       <c r="J57" s="1" t="n">
-        <v>109.0</v>
+        <v>167.0</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>0.78</v>
+        <v>0.5</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>0.0642</v>
-      </c>
-      <c r="N57" s="2" t="n">
-        <v>0.6471</v>
+        <v>0.012</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -3510,7 +3468,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>"ราคาทอง ร้านทองเยาวราช"</t>
+          <t>"แอปทอง ออนไลน์"</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3574,7 +3532,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>"ร้านทอง เปิดวันอาทิตย์"</t>
+          <t>"ร้านทอง ฟิวเจอร์"</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3608,26 +3566,22 @@
         </is>
       </c>
       <c r="I59" s="1" t="n">
-        <v>0.0</v>
+        <v>13.33</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>0.0</v>
+        <v>80.0</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+        <v>1.21</v>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>0.1375</v>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>0.625</v>
       </c>
     </row>
     <row r="60">
@@ -3638,12 +3592,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>[aurora]</t>
+          <t>"ร้านทองแท้"</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Exact match</t>
+          <t>Phrase match</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3672,22 +3626,22 @@
         </is>
       </c>
       <c r="I60" s="1" t="n">
-        <v>33.41</v>
+        <v>69.52</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>255.0</v>
+        <v>345.0</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>144.0</v>
+        <v>47.0</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>0.23</v>
+        <v>1.48</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>0.5647</v>
+        <v>0.1362</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.9749</v>
+        <v>0.7407</v>
       </c>
     </row>
     <row r="61">
@@ -3698,12 +3652,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>"ร้านทองแท้"</t>
+          <t>[Bangkok Golds]</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Phrase match</t>
+          <t>Exact match</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3732,22 +3686,24 @@
         </is>
       </c>
       <c r="I61" s="1" t="n">
-        <v>0.69</v>
+        <v>1.18</v>
       </c>
       <c r="J61" s="1" t="n">
-        <v>19.0</v>
+        <v>4.0</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>0.23</v>
+        <v>1.18</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>0.1579</v>
-      </c>
-      <c r="N61" s="2" t="n">
-        <v>1.0</v>
+        <v>0.25</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -3758,7 +3714,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>"www hua seng heng com"</t>
+          <t>"ร้านทอง โลตัส"</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3792,26 +3748,22 @@
         </is>
       </c>
       <c r="I62" s="1" t="n">
-        <v>0.0</v>
+        <v>0.77</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>0.0</v>
+        <v>38.0</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+        <v>0.77</v>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>0.0263</v>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>0.6667</v>
       </c>
     </row>
     <row r="63">
@@ -3822,12 +3774,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>[ฮั่วเซ่งเฮง]</t>
+          <t>"ซื้อทองออนไลน์"</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Exact match</t>
+          <t>Phrase match</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3856,22 +3808,22 @@
         </is>
       </c>
       <c r="I63" s="1" t="n">
-        <v>0.46</v>
+        <v>6.88</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>85.0</v>
+        <v>66.0</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>0.46</v>
+        <v>1.72</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>0.0118</v>
+        <v>0.0606</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.0</v>
+        <v>0.7969</v>
       </c>
     </row>
     <row r="64">
@@ -3882,12 +3834,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>"ร้านทอง ฟิวเจอร์"</t>
+          <t>[ห้าง ทอง เยาวราช กรุงเทพ ใกล้ ฉัน]</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Phrase match</t>
+          <t>Exact match</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3919,7 +3871,7 @@
         <v>0.0</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
       <c r="K64" s="1" t="n">
         <v>0.0</v>
@@ -3927,10 +3879,8 @@
       <c r="L64" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+      <c r="M64" s="2" t="n">
+        <v>0.0</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -3946,12 +3896,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>[แม่ทองสุก]</t>
+          <t>"ร้านทองเยาวราช"</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Exact match</t>
+          <t>Phrase match</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3980,24 +3930,22 @@
         </is>
       </c>
       <c r="I65" s="1" t="n">
-        <v>0.0</v>
+        <v>11.17</v>
       </c>
       <c r="J65" s="1" t="n">
-        <v>2.0</v>
+        <v>539.0</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>0.0</v>
+        <v>1.02</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+        <v>0.0204</v>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>0.5778</v>
       </c>
     </row>
     <row r="66">
@@ -4008,7 +3956,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>"สร้อยทอง 2 สลึง"</t>
+          <t>"สมาคมทองคำ"</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4023,7 +3971,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Generic</t>
+          <t>Brand</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4042,22 +3990,26 @@
         </is>
       </c>
       <c r="I66" s="1" t="n">
-        <v>0.38</v>
+        <v>0.0</v>
       </c>
       <c r="J66" s="1" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="M66" s="2" t="n">
-        <v>0.0833</v>
-      </c>
-      <c r="N66" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.0</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -4068,12 +4020,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>"แบรนด์ aurora"</t>
+          <t>[ห้างทองฮั่วเซ่งเฮง]</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Phrase match</t>
+          <t>Exact match</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4083,17 +4035,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Generic</t>
+          <t>Brand</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Eligible</t>
+          <t>Limited</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t/>
+          <t>low quality</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4105,7 +4057,7 @@
         <v>0.0</v>
       </c>
       <c r="J67" s="1" t="n">
-        <v>0.0</v>
+        <v>130.0</v>
       </c>
       <c r="K67" s="1" t="n">
         <v>0.0</v>
@@ -4113,15 +4065,11 @@
       <c r="L67" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+      <c r="M67" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>0.0</v>
       </c>
     </row>
     <row r="68">
@@ -4132,7 +4080,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>"ราคาทองวันนี้"</t>
+          <t>"ร้านทองออนไลน์"</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4166,22 +4114,22 @@
         </is>
       </c>
       <c r="I68" s="1" t="n">
-        <v>211.12</v>
+        <v>0.0</v>
       </c>
       <c r="J68" s="1" t="n">
-        <v>2017.0</v>
+        <v>1.0</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>318.0</v>
+        <v>0.0</v>
       </c>
       <c r="L68" s="1" t="n">
-        <v>0.66</v>
+        <v>0.0</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>0.1577</v>
+        <v>0.0</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.4712</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="69">
@@ -4192,12 +4140,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>[ห้าง ทอง ออ โร ร่า ใกล้ ฉัน]</t>
+          <t>"ทองสมาคม"</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Exact match</t>
+          <t>Phrase match</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4229,7 +4177,7 @@
         <v>0.0</v>
       </c>
       <c r="J69" s="1" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="K69" s="1" t="n">
         <v>0.0</v>
@@ -4237,22 +4185,26 @@
       <c r="L69" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="M69" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N69" s="2" t="n">
-        <v>0.5</v>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Enabled</t>
+          <t>Paused</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>"ทองสมาคม"</t>
+          <t>"ร้านทอ"</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4272,12 +4224,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Eligible</t>
+          <t>Paused</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t/>
+          <t>paused</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4316,12 +4268,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ร้าน ทอง ใกล้ ฉัน</t>
+          <t>"ร้านทองใกล้ฉัน"</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Broad match</t>
+          <t>Phrase match</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4350,22 +4302,22 @@
         </is>
       </c>
       <c r="I71" s="1" t="n">
-        <v>19.63</v>
+        <v>54.91</v>
       </c>
       <c r="J71" s="1" t="n">
-        <v>696.0</v>
+        <v>418.0</v>
       </c>
       <c r="K71" s="1" t="n">
-        <v>62.0</v>
+        <v>20.0</v>
       </c>
       <c r="L71" s="1" t="n">
-        <v>0.32</v>
+        <v>2.75</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>0.0891</v>
+        <v>0.0478</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.3867</v>
+        <v>0.6026</v>
       </c>
     </row>
     <row r="72">
@@ -4376,12 +4328,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>[ห้าง ทอง เยาวราช กรุงเทพ]</t>
+          <t>"ห้างทองเยาวราช ราคา"</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Exact match</t>
+          <t>Phrase match</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4425,7 +4377,7 @@
         <v>0.0</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>1.0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="73">
@@ -4473,7 +4425,7 @@
         <v>0.0</v>
       </c>
       <c r="J73" s="1" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="K73" s="1" t="n">
         <v>0.0</v>
@@ -4481,15 +4433,11 @@
       <c r="L73" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+      <c r="M73" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N73" s="2" t="n">
+        <v>0.0</v>
       </c>
     </row>
     <row r="74">
@@ -4500,12 +4448,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>"แหวน ทอง 1 กรัม aurora"</t>
+          <t>ร้าน ทอง ใกล้ ฉัน</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Phrase match</t>
+          <t>Broad match</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4515,7 +4463,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Generic</t>
+          <t>Brand</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4534,26 +4482,22 @@
         </is>
       </c>
       <c r="I74" s="1" t="n">
-        <v>0.0</v>
+        <v>339.9</v>
       </c>
       <c r="J74" s="1" t="n">
-        <v>0.0</v>
+        <v>4255.0</v>
       </c>
       <c r="K74" s="1" t="n">
-        <v>0.0</v>
+        <v>445.0</v>
       </c>
       <c r="L74" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+        <v>0.76</v>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>0.1046</v>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>0.4163</v>
       </c>
     </row>
     <row r="75">
@@ -4564,7 +4508,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>"ห้าง ทอง ทอง เยาวราช"</t>
+          <t>"ห้างทองเยาวราช ราคาทอง"</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4601,7 +4545,7 @@
         <v>0.0</v>
       </c>
       <c r="J75" s="1" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="K75" s="1" t="n">
         <v>0.0</v>
@@ -4609,11 +4553,15 @@
       <c r="L75" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="M75" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N75" s="2" t="n">
-        <v>0.5</v>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -4658,22 +4606,22 @@
         </is>
       </c>
       <c r="I76" s="1" t="n">
-        <v>604.37</v>
+        <v>2433.86</v>
       </c>
       <c r="J76" s="1" t="n">
-        <v>7805.0</v>
+        <v>26439.0</v>
       </c>
       <c r="K76" s="1" t="n">
-        <v>1167.0</v>
+        <v>3633.0</v>
       </c>
       <c r="L76" s="1" t="n">
-        <v>0.52</v>
+        <v>0.67</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>0.1495</v>
+        <v>0.1374</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.5072</v>
+        <v>0.5211</v>
       </c>
     </row>
     <row r="77">
@@ -4718,22 +4666,22 @@
         </is>
       </c>
       <c r="I77" s="1" t="n">
-        <v>604.37</v>
+        <v>2433.86</v>
       </c>
       <c r="J77" s="1" t="n">
-        <v>7805.0</v>
+        <v>26439.0</v>
       </c>
       <c r="K77" s="1" t="n">
-        <v>1167.0</v>
+        <v>3633.0</v>
       </c>
       <c r="L77" s="1" t="n">
-        <v>0.52</v>
+        <v>0.67</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>0.1495</v>
+        <v>0.1374</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.5072</v>
+        <v>0.5211</v>
       </c>
     </row>
     <row r="78">
@@ -4778,19 +4726,19 @@
         </is>
       </c>
       <c r="I78" s="1" t="n">
-        <v>604.37</v>
+        <v>2433.86</v>
       </c>
       <c r="J78" s="1" t="n">
-        <v>7805.0</v>
+        <v>26439.0</v>
       </c>
       <c r="K78" s="1" t="n">
-        <v>1167.0</v>
+        <v>3633.0</v>
       </c>
       <c r="L78" s="1" t="n">
-        <v>0.52</v>
+        <v>0.67</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>0.1495</v>
+        <v>0.1374</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
@@ -5032,22 +4980,22 @@
         </is>
       </c>
       <c r="I82" s="1" t="n">
-        <v>1751.57</v>
+        <v>5311.5</v>
       </c>
       <c r="J82" s="1" t="n">
-        <v>10032.0</v>
+        <v>54035.0</v>
       </c>
       <c r="K82" s="1" t="n">
-        <v>1600.0</v>
+        <v>5908.0</v>
       </c>
       <c r="L82" s="1" t="n">
-        <v>1.09</v>
+        <v>0.9</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>0.1595</v>
+        <v>0.1093</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.5072</v>
+        <v>0.5211</v>
       </c>
     </row>
     <row r="83">
@@ -5092,19 +5040,19 @@
         </is>
       </c>
       <c r="I83" s="1" t="n">
-        <v>1147.2</v>
+        <v>2877.64</v>
       </c>
       <c r="J83" s="1" t="n">
-        <v>2227.0</v>
+        <v>27596.0</v>
       </c>
       <c r="K83" s="1" t="n">
-        <v>433.0</v>
+        <v>2275.0</v>
       </c>
       <c r="L83" s="1" t="n">
-        <v>2.65</v>
+        <v>1.26</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>0.1944</v>
+        <v>0.0824</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -5154,22 +5102,22 @@
         </is>
       </c>
       <c r="I84" s="1" t="n">
-        <v>604.37</v>
+        <v>2433.86</v>
       </c>
       <c r="J84" s="1" t="n">
-        <v>7805.0</v>
+        <v>26439.0</v>
       </c>
       <c r="K84" s="1" t="n">
-        <v>1167.0</v>
+        <v>3633.0</v>
       </c>
       <c r="L84" s="1" t="n">
-        <v>0.52</v>
+        <v>0.67</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>0.1495</v>
+        <v>0.1374</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.5072</v>
+        <v>0.5211</v>
       </c>
     </row>
   </sheetData>
